--- a/TP3/bases/logit_2025_coeficientes.xlsx
+++ b/TP3/bases/logit_2025_coeficientes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.06015439561929634</v>
+        <v>-0.06015439561929631</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01344987971790064</v>
+        <v>0.01344987971790062</v>
       </c>
       <c r="D2" t="n">
         <v>0.9416191404901719</v>
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.00290202374509945</v>
+        <v>-0.002902023745099427</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02541191727908952</v>
+        <v>0.02541191727909357</v>
       </c>
       <c r="D3" t="n">
         <v>0.9971021830554135</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0005731595546954785</v>
+        <v>-0.0005731595546954826</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02524946800663272</v>
+        <v>0.02524946800663674</v>
       </c>
       <c r="D4" t="n">
         <v>0.999427004669865</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01235200078858994</v>
+        <v>-0.01235200078858992</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004675791495721777</v>
+        <v>0.004675791495721787</v>
       </c>
       <c r="D5" t="n">
         <v>0.987723972045931</v>
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1545590966493622</v>
+        <v>0.1545590966493624</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1034028664959954</v>
+        <v>0.1034028664959955</v>
       </c>
       <c r="D6" t="n">
         <v>1.167143250274878</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4210826304588726</v>
+        <v>0.4210826304588727</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03386635310000891</v>
+        <v>0.03386635310000893</v>
       </c>
       <c r="D7" t="n">
         <v>1.523610169814925</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.02534739375196458</v>
+        <v>-0.02534739375196442</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03911751020541381</v>
+        <v>0.03911751020541401</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9749711543032303</v>
+        <v>0.9749711543032304</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5041398353076679</v>
+        <v>0.504139835307668</v>
       </c>
       <c r="C9" t="n">
         <v>0.03703117175923645</v>
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.05211966771729761</v>
+        <v>-0.05211966771729709</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09627890861227176</v>
+        <v>0.09627890861227163</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9492152696215255</v>
+        <v>0.9492152696215259</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-2.806005054699695</v>
+        <v>-2.806005054699698</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5103075244318018</v>
+        <v>0.5103075244318045</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06044598910761657</v>
+        <v>0.06044598910761635</v>
       </c>
     </row>
   </sheetData>
